--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6261-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6261-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75EC8641-B05D-4EFC-AF49-6E8E9CBCB2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E33E1037-3DA5-4C23-8D4E-722A3FA90BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{A43D508D-EC52-425D-9D3C-2019B41598D7}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{22602005-F83A-4992-AA7D-F74F81346D91}"/>
   </bookViews>
   <sheets>
     <sheet name="6261-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1514,28 +1514,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9680B3-89E2-4602-AF7A-9DEEF1870EFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72EE8347-945C-4602-A308-AF48E6AB13A4}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1605,7 +1605,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1725,7 +1725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2024</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2023</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2022</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>9.0399999999999991</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2021</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2020</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2019</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>8.01</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2018</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>7.59</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2017</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2016</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2015</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2014</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2013</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2012</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>9.06</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2011</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2010</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2009</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2008</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2007</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2006</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2005</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2004</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>2003</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2002</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>2001</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>2000</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36" t="s">
         <v>58</v>
       </c>
